--- a/data/trans_dic/IP1003-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen Alergias crónicas</t>
+          <t>Menores que padecen Alergias crónicas (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,04</t>
+          <t>0,0; 8,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 13,94</t>
+          <t>1,91; 13,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,56; 16,02</t>
+          <t>3,45; 15,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 12,36</t>
+          <t>2,47; 11,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 13,04</t>
+          <t>2,37; 13,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,71; 14,58</t>
+          <t>3,01; 17,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 14,13</t>
+          <t>2,78; 14,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 12,72</t>
+          <t>2,45; 12,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 8,36</t>
+          <t>1,83; 8,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 12,18</t>
+          <t>3,58; 12,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,85</t>
+          <t>4,47; 13,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 10,06</t>
+          <t>3,26; 10,04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 6,81</t>
+          <t>1,25; 7,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 12,2</t>
+          <t>3,51; 12,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 10,11</t>
+          <t>1,94; 9,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 10,88</t>
+          <t>2,34; 11,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 8,68</t>
+          <t>1,84; 8,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,09; 10,72</t>
+          <t>3,35; 11,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 9,22</t>
+          <t>2,0; 9,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 10,41</t>
+          <t>2,51; 11,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,61</t>
+          <t>2,33; 6,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 10,04</t>
+          <t>4,12; 10,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,01</t>
+          <t>2,76; 8,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,39; 9,04</t>
+          <t>3,36; 9,03</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,7 +997,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 14,95</t>
+          <t>3,16; 14,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1006,52 +1007,52 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 7,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,05</t>
+          <t>0,0; 6,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 10,15</t>
+          <t>1,66; 9,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,76</t>
+          <t>0,91; 8,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 11,12</t>
+          <t>1,98; 11,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 12,81</t>
+          <t>2,78; 12,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 9,77</t>
+          <t>3,04; 9,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,68</t>
+          <t>0,99; 5,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,14</t>
+          <t>1,58; 7,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,4</t>
+          <t>1,54; 7,09</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 18,59</t>
+          <t>5,87; 17,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 12,11</t>
+          <t>1,99; 12,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,09; 12,94</t>
+          <t>3,17; 12,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 13,5</t>
+          <t>1,55; 12,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,32; 18,94</t>
+          <t>6,33; 17,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 12,8</t>
+          <t>3,37; 13,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 14,51</t>
+          <t>3,56; 14,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 15,88</t>
+          <t>1,84; 16,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,59; 15,94</t>
+          <t>7,83; 15,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 10,53</t>
+          <t>3,6; 9,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 11,15</t>
+          <t>4,39; 11,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 11,3</t>
+          <t>2,63; 11,59</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 23,38</t>
+          <t>5,51; 24,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 16,45</t>
+          <t>1,95; 16,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,34</t>
+          <t>0,0; 10,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 11,23</t>
+          <t>1,33; 11,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 14,58</t>
+          <t>1,58; 14,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,47</t>
+          <t>1,43; 13,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,27</t>
+          <t>0,0; 7,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,86; 27,41</t>
+          <t>2,88; 25,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,52; 15,04</t>
+          <t>4,55; 15,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 11,62</t>
+          <t>3,07; 11,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,68</t>
+          <t>0,0; 5,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 16,57</t>
+          <t>3,42; 16,29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,57</t>
+          <t>1,25; 11,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,43</t>
+          <t>2,21; 13,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,2; 16,09</t>
+          <t>3,55; 15,98</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,69; 23,36</t>
+          <t>7,33; 24,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,12; 21,16</t>
+          <t>7,3; 20,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,9; 20,5</t>
+          <t>5,48; 19,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,49; 21,03</t>
+          <t>5,71; 20,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,02; 28,51</t>
+          <t>9,44; 28,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,5</t>
+          <t>5,44; 13,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,76; 13,86</t>
+          <t>4,75; 14,02</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,78; 16,32</t>
+          <t>5,68; 15,44</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,48; 23,26</t>
+          <t>10,86; 23,94</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 7,71</t>
+          <t>1,63; 7,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,9</t>
+          <t>1,97; 7,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,94</t>
+          <t>0,98; 5,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,36</t>
+          <t>4,5; 13,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 10,08</t>
+          <t>2,99; 9,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 8,61</t>
+          <t>2,46; 8,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,33</t>
+          <t>0,92; 5,67</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,05; 20,73</t>
+          <t>8,75; 20,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,72</t>
+          <t>2,87; 6,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,05</t>
+          <t>2,78; 7,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,67</t>
+          <t>1,23; 4,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,5; 15,12</t>
+          <t>7,77; 14,96</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,37; 9,49</t>
+          <t>3,25; 9,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,97</t>
+          <t>1,22; 5,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,09; 7,44</t>
+          <t>2,48; 8,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,37</t>
+          <t>0,44; 4,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,29; 10,75</t>
+          <t>4,36; 10,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,1; 9,49</t>
+          <t>3,04; 9,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,73</t>
+          <t>2,52; 7,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,01; 7,87</t>
+          <t>2,19; 8,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,51; 8,91</t>
+          <t>4,6; 8,7</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,18</t>
+          <t>2,66; 6,18</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,52</t>
+          <t>2,86; 6,56</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,41</t>
+          <t>1,63; 5,21</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,59; 7,46</t>
+          <t>4,71; 7,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,45; 6,18</t>
+          <t>3,43; 6,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,08</t>
+          <t>3,39; 6,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,18</t>
+          <t>4,0; 7,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,44</t>
+          <t>5,56; 8,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,81; 7,7</t>
+          <t>4,64; 7,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,7</t>
+          <t>3,92; 6,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,45; 10,45</t>
+          <t>6,47; 10,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,46; 7,61</t>
+          <t>5,47; 7,64</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,52</t>
+          <t>4,53; 6,5</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,01; 5,92</t>
+          <t>4,04; 5,94</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,2</t>
+          <t>5,81; 8,36</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen Alergias crónicas (tasa de respuesta: 99,75%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3465</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4768</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4430</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3753</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4694</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4563</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>5016</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8156</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9462</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>8993</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4236</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1013; 7103</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1982; 8857</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1813; 8761</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1427; 7850</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1829; 10411</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1795; 9525</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1947; 9703</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2059; 9719</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>4077; 13883</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5444; 16294</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4972; 15327</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3726</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5062</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7586</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6823</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5418</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>6886</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8792</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>14130</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>10480</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>14472</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1266; 7694</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3652; 12508</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2022; 9977</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2945; 14571</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2003; 9397</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3721; 12900</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2203; 10721</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3156; 14103</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4901; 14380</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>8859; 21519</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5919; 17331</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>8461; 22737</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1419</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1458</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3524</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3966</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>8111</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3698</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4982</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4555</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2133; 10079</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4969</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3658</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1165; 6756</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>645; 6087</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1385; 7808</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1867; 8196</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>4199; 13526</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1368; 8028</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2160; 10658</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1934; 8893</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>8405</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4081</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5063</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3544</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9012</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5938</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6490</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5052</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>17417</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>10019</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>11553</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>8596</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4397; 13198</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1546; 9608</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2442; 9364</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1075; 8967</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>5010; 14073</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2774; 10914</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2892; 11639</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>1437; 13019</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>12051; 24353</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>5766; 15947</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>6947; 17518</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3890; 17109</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>5278</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>662</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2385</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2627</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4375</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>7663</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>6075</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2307; 10355</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>855; 7434</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4691</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>458; 3924</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>709; 6649</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>661; 6142</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3577</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1174; 10306</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>3941; 13398</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2764; 10298</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5148</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2570; 12253</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2740</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3191</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6778</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7510</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>6892</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6650</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>9669</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>10249</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>10083</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>11062</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>16447</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>698; 6225</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>1237; 7330</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1925; 8671</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>3382; 11136</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>4360; 12098</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>3300; 11827</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>3298; 11985</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>5305; 15858</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>6304; 15987</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>5518; 16300</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>6366; 17295</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>11116; 24501</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>4909</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5804</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9892</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>7609</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3524</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>21216</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>12519</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>12964</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>7169</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>31109</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2101; 9209</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2730; 10058</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1344; 8096</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>5609; 16346</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4050; 13173</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3585; 12823</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1324; 8174</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>13659; 32189</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>7586; 18401</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>7920; 20206</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3471; 13715</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>21785; 41974</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>9243</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4695</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>7062</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>11596</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>9257</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>7507</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>6907</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>20838</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>13952</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>14569</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>8991</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>5139; 14536</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2015; 9126</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>4070; 13342</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>581; 5810</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>7147; 17854</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>5204; 15548</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>4310; 12888</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>3432; 13276</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>14826; 28017</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>8945; 20771</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>9587; 21966</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>4698; 15034</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>40639</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>33189</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>32132</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>36603</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>45668</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>38600</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>62635</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>90606</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>78857</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>70732</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>99238</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>32109; 51320</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>24255; 43089</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>23846; 43540</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>26562; 47281</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>40194; 61202</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>34688; 57298</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>29223; 50166</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>49192; 80052</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>76829; 107294</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>65827; 94505</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>58482; 86083</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>82784; 119073</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1003-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Provincia-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,06</t>
+          <t>0,0; 8,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 13,41</t>
+          <t>2,43; 15,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,45; 15,44</t>
+          <t>3,54; 16,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 11,96</t>
+          <t>2,65; 12,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 13,04</t>
+          <t>2,5; 14,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 17,13</t>
+          <t>2,87; 16,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 14,78</t>
+          <t>2,91; 15,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 12,23</t>
+          <t>2,47; 12,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 8,62</t>
+          <t>1,86; 9,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,58; 12,21</t>
+          <t>3,7; 12,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,47; 13,37</t>
+          <t>4,48; 13,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 10,04</t>
+          <t>3,18; 9,89</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,58</t>
+          <t>1,77; 7,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 12,02</t>
+          <t>3,84; 12,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,6</t>
+          <t>2,03; 9,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 11,56</t>
+          <t>2,04; 11,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 8,64</t>
+          <t>2,24; 8,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 11,6</t>
+          <t>3,02; 10,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 9,72</t>
+          <t>2,08; 10,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 11,21</t>
+          <t>2,57; 11,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,84</t>
+          <t>2,41; 6,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 10,0</t>
+          <t>3,98; 9,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 8,09</t>
+          <t>2,75; 8,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,03</t>
+          <t>3,28; 9,29</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,16; 14,91</t>
+          <t>3,26; 14,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,29</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,69</t>
+          <t>0,0; 7,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,28</t>
+          <t>0,0; 5,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 9,61</t>
+          <t>1,64; 9,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,62</t>
+          <t>0,91; 8,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,17</t>
+          <t>1,97; 11,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 12,2</t>
+          <t>2,2; 11,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,81</t>
+          <t>2,98; 9,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 5,79</t>
+          <t>0,71; 5,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 7,79</t>
+          <t>1,57; 7,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,09</t>
+          <t>1,54; 7,18</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,87; 17,63</t>
+          <t>6,34; 17,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 12,36</t>
+          <t>1,92; 11,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 12,17</t>
+          <t>3,02; 12,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 12,9</t>
+          <t>1,23; 12,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,33; 17,79</t>
+          <t>6,84; 19,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 13,27</t>
+          <t>3,8; 13,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,56; 14,34</t>
+          <t>4,24; 14,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 16,66</t>
+          <t>1,85; 17,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 15,82</t>
+          <t>7,95; 15,84</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,6; 9,97</t>
+          <t>3,58; 10,37</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 11,08</t>
+          <t>4,37; 11,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 11,59</t>
+          <t>2,56; 11,26</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 24,74</t>
+          <t>5,45; 24,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 16,93</t>
+          <t>2,05; 17,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,8</t>
+          <t>0,0; 9,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 11,37</t>
+          <t>1,32; 12,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 14,83</t>
+          <t>1,58; 14,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 13,32</t>
+          <t>1,43; 13,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,72</t>
+          <t>0,0; 8,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 25,31</t>
+          <t>2,86; 26,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,55; 15,45</t>
+          <t>4,8; 15,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,07; 11,44</t>
+          <t>3,15; 12,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,73</t>
+          <t>0,0; 5,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 16,29</t>
+          <t>3,45; 17,47</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,11</t>
+          <t>1,25; 11,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,21; 13,09</t>
+          <t>2,13; 12,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,55; 15,98</t>
+          <t>3,72; 17,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,33; 24,12</t>
+          <t>7,52; 23,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,3; 20,25</t>
+          <t>7,38; 21,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,48; 19,63</t>
+          <t>6,06; 20,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,71; 20,76</t>
+          <t>5,64; 20,83</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,44; 28,22</t>
+          <t>9,92; 28,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,44; 13,81</t>
+          <t>5,43; 13,37</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,75; 14,02</t>
+          <t>5,16; 13,94</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,68; 15,44</t>
+          <t>5,69; 15,97</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,86; 23,94</t>
+          <t>10,96; 23,11</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,16</t>
+          <t>1,62; 7,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 7,25</t>
+          <t>1,96; 7,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,89</t>
+          <t>0,96; 5,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 13,13</t>
+          <t>4,31; 13,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 9,71</t>
+          <t>3,08; 10,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 8,8</t>
+          <t>2,66; 8,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,67</t>
+          <t>0,91; 5,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,75; 20,63</t>
+          <t>8,78; 21,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,96</t>
+          <t>2,89; 7,39</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,1</t>
+          <t>2,83; 6,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,87</t>
+          <t>1,31; 4,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,77; 14,96</t>
+          <t>7,93; 15,48</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,25; 9,21</t>
+          <t>3,33; 9,44</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,54</t>
+          <t>1,19; 5,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,13</t>
+          <t>2,13; 7,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,41</t>
+          <t>0,46; 4,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,36; 10,88</t>
+          <t>4,49; 11,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,04; 9,08</t>
+          <t>3,12; 8,78</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,54</t>
+          <t>2,39; 7,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,19; 8,47</t>
+          <t>2,04; 8,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,7</t>
+          <t>4,6; 8,79</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,18</t>
+          <t>2,64; 6,21</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,56</t>
+          <t>2,84; 6,44</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,21</t>
+          <t>1,6; 5,15</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,71; 7,54</t>
+          <t>4,53; 7,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,1</t>
+          <t>3,53; 6,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,39; 6,18</t>
+          <t>3,35; 5,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,12</t>
+          <t>4,13; 7,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,47</t>
+          <t>5,42; 8,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,66</t>
+          <t>4,68; 7,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,74</t>
+          <t>3,98; 6,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,47; 10,53</t>
+          <t>6,48; 10,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,47; 7,64</t>
+          <t>5,52; 7,67</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 6,5</t>
+          <t>4,51; 6,57</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,94</t>
+          <t>3,97; 5,9</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,36</t>
+          <t>5,56; 8,33</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4236</t>
+          <t>0; 4357</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1013; 7103</t>
+          <t>1289; 7962</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1982; 8857</t>
+          <t>2030; 9428</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1813; 8761</t>
+          <t>1941; 9233</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1427; 7850</t>
+          <t>1504; 8554</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1829; 10411</t>
+          <t>1741; 9928</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1795; 9525</t>
+          <t>1875; 10028</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1947; 9703</t>
+          <t>1960; 9775</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2059; 9719</t>
+          <t>2096; 10216</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4077; 13883</t>
+          <t>4210; 13846</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5444; 16294</t>
+          <t>5456; 16228</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4972; 15327</t>
+          <t>4861; 15101</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1266; 7694</t>
+          <t>1796; 7516</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3652; 12508</t>
+          <t>3993; 12660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2022; 9977</t>
+          <t>2111; 10225</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2945; 14571</t>
+          <t>2576; 14067</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2003; 9397</t>
+          <t>2440; 9778</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3721; 12900</t>
+          <t>3358; 12103</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2203; 10721</t>
+          <t>2292; 11148</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3156; 14103</t>
+          <t>3237; 13866</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4901; 14380</t>
+          <t>5060; 14278</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8859; 21519</t>
+          <t>8577; 20719</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5919; 17331</t>
+          <t>5893; 17257</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8461; 22737</t>
+          <t>8254; 23401</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2133; 10079</t>
+          <t>2203; 9596</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4969</t>
+          <t>0; 4834</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5138</t>
+          <t>0; 5155</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3658</t>
+          <t>0; 2954</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1165; 6756</t>
+          <t>1156; 6769</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>645; 6087</t>
+          <t>642; 6063</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1385; 7808</t>
+          <t>1376; 7837</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1867; 8196</t>
+          <t>1476; 7889</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4199; 13526</t>
+          <t>4112; 13655</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1368; 8028</t>
+          <t>990; 7980</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2160; 10658</t>
+          <t>2143; 9618</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1934; 8893</t>
+          <t>1938; 9000</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4397; 13198</t>
+          <t>4743; 13443</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1546; 9608</t>
+          <t>1496; 9304</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2442; 9364</t>
+          <t>2323; 9255</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1075; 8967</t>
+          <t>854; 8799</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5010; 14073</t>
+          <t>5414; 15040</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2774; 10914</t>
+          <t>3121; 10884</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2892; 11639</t>
+          <t>3443; 11443</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1437; 13019</t>
+          <t>1442; 13401</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12051; 24353</t>
+          <t>12248; 24382</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5766; 15947</t>
+          <t>5723; 16598</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6947; 17518</t>
+          <t>6906; 18267</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3890; 17109</t>
+          <t>3777; 16624</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2307; 10355</t>
+          <t>2283; 10066</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>855; 7434</t>
+          <t>899; 7469</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4691</t>
+          <t>0; 4008</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>458; 3924</t>
+          <t>454; 4175</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>709; 6649</t>
+          <t>709; 6332</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>661; 6142</t>
+          <t>658; 6127</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3577</t>
+          <t>0; 3996</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1174; 10306</t>
+          <t>1166; 10852</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3941; 13398</t>
+          <t>4159; 13105</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2764; 10298</t>
+          <t>2834; 10798</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5148</t>
+          <t>0; 5128</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2570; 12253</t>
+          <t>2594; 13145</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>698; 6225</t>
+          <t>700; 6232</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1237; 7330</t>
+          <t>1194; 7084</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1925; 8671</t>
+          <t>2019; 9765</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3382; 11136</t>
+          <t>3471; 11013</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4360; 12098</t>
+          <t>4408; 12817</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3300; 11827</t>
+          <t>3648; 12156</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3298; 11985</t>
+          <t>3256; 12028</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5305; 15858</t>
+          <t>5571; 15903</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6304; 15987</t>
+          <t>6286; 15484</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5518; 16300</t>
+          <t>6000; 16199</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6366; 17295</t>
+          <t>6375; 17893</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11116; 24501</t>
+          <t>11214; 23650</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2101; 9209</t>
+          <t>2086; 9343</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2730; 10058</t>
+          <t>2722; 10920</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1344; 8096</t>
+          <t>1317; 8116</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5609; 16346</t>
+          <t>5360; 16298</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4050; 13173</t>
+          <t>4184; 13843</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3585; 12823</t>
+          <t>3874; 12349</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1324; 8174</t>
+          <t>1316; 7543</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13659; 32189</t>
+          <t>13703; 33343</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7586; 18401</t>
+          <t>7636; 19531</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7920; 20206</t>
+          <t>8052; 19500</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3471; 13715</t>
+          <t>3695; 12851</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21785; 41974</t>
+          <t>22248; 43424</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5139; 14536</t>
+          <t>5259; 14903</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2015; 9126</t>
+          <t>1962; 8929</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4070; 13342</t>
+          <t>3499; 11825</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>581; 5810</t>
+          <t>601; 5656</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7147; 17854</t>
+          <t>7371; 18141</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5204; 15548</t>
+          <t>5349; 15035</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4310; 12888</t>
+          <t>4083; 12585</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3432; 13276</t>
+          <t>3198; 13183</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14826; 28017</t>
+          <t>14826; 28285</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8945; 20771</t>
+          <t>8860; 20858</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9587; 21966</t>
+          <t>9519; 21580</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4698; 15034</t>
+          <t>4606; 14856</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>32109; 51320</t>
+          <t>30846; 51436</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>24255; 43089</t>
+          <t>24901; 44335</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23846; 43540</t>
+          <t>23611; 41695</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26562; 47281</t>
+          <t>27416; 50068</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>40194; 61202</t>
+          <t>39158; 60760</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34688; 57298</t>
+          <t>35045; 56959</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29223; 50166</t>
+          <t>29652; 50237</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>49192; 80052</t>
+          <t>49293; 79927</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>76829; 107294</t>
+          <t>77445; 107716</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>65827; 94505</t>
+          <t>65552; 95580</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>58482; 86083</t>
+          <t>57546; 85532</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>82784; 119073</t>
+          <t>79215; 118587</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1003-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1003-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,23%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,55%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,4%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,54%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,31%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,29</t>
+          <t>2,38; 13,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 15,03</t>
+          <t>2,71; 14,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,54; 16,43</t>
+          <t>2,81; 14,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 12,6</t>
+          <t>2,78; 14,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 14,21</t>
+          <t>0,0; 8,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 16,34</t>
+          <t>2,07; 13,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 15,56</t>
+          <t>3,56; 16,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 12,32</t>
+          <t>3,25; 14,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 9,06</t>
+          <t>1,95; 8,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 12,18</t>
+          <t>3,76; 12,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 13,32</t>
+          <t>4,16; 12,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 9,89</t>
+          <t>3,82; 11,47</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>3,67%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>7,02%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,87%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,14%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 7,4</t>
+          <t>1,84; 8,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 12,16</t>
+          <t>3,09; 10,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,84</t>
+          <t>2,14; 9,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 11,16</t>
+          <t>2,24; 10,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,99</t>
+          <t>1,23; 6,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,02; 10,89</t>
+          <t>3,39; 12,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 10,11</t>
+          <t>2,13; 10,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 11,02</t>
+          <t>4,21; 14,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,79</t>
+          <t>2,38; 6,61</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,63</t>
+          <t>4,15; 10,04</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 8,06</t>
+          <t>2,94; 8,01</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 9,29</t>
+          <t>4,13; 10,11</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>7,51%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,08%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,18%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 14,2</t>
+          <t>1,65; 10,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,91; 8,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,71</t>
+          <t>2,01; 11,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,07</t>
+          <t>2,97; 13,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 9,63</t>
+          <t>3,26; 14,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,59</t>
+          <t>0,0; 7,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 11,21</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 11,75</t>
+          <t>0,0; 5,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 9,9</t>
+          <t>3,42; 9,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,75</t>
+          <t>0,99; 6,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,03</t>
+          <t>1,55; 7,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,18</t>
+          <t>1,59; 7,52</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,39%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,22%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7,99%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,81%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>11,23%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,25%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6,58%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>7,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,99%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 17,96</t>
+          <t>6,32; 18,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,97</t>
+          <t>3,44; 12,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 12,03</t>
+          <t>4,33; 14,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 12,66</t>
+          <t>1,78; 17,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,84; 19,01</t>
+          <t>6,51; 18,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 13,23</t>
+          <t>1,89; 12,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 14,1</t>
+          <t>3,09; 12,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 17,15</t>
+          <t>1,33; 14,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,95; 15,84</t>
+          <t>7,59; 15,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 10,37</t>
+          <t>3,69; 10,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 11,55</t>
+          <t>4,49; 11,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 11,26</t>
+          <t>2,72; 11,93</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,7%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>12,61%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7,35%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 24,05</t>
+          <t>1,58; 14,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 17,01</t>
+          <t>1,44; 13,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,23</t>
+          <t>0,0; 8,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 12,1</t>
+          <t>2,92; 22,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 14,12</t>
+          <t>5,48; 23,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 13,29</t>
+          <t>1,98; 16,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,62</t>
+          <t>0,0; 6,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,86; 26,65</t>
+          <t>1,38; 11,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,8; 15,12</t>
+          <t>4,52; 15,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 12,0</t>
+          <t>3,03; 11,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,71</t>
+          <t>0,0; 5,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,45; 17,47</t>
+          <t>3,28; 15,44</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12,57%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11,44%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11,52%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18,07%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4,89%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5,7%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8,13%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14,68%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12,57%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>11,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>11,52%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,12</t>
+          <t>7,12; 21,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,65</t>
+          <t>5,9; 20,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,72; 17,99</t>
+          <t>5,49; 21,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,52; 23,85</t>
+          <t>10,67; 29,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,38; 21,46</t>
+          <t>1,25; 11,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,06; 20,18</t>
+          <t>2,2; 12,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,64; 20,83</t>
+          <t>3,2; 16,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,92; 28,3</t>
+          <t>8,09; 24,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,43; 13,37</t>
+          <t>5,18; 13,5</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,16; 13,94</t>
+          <t>4,76; 13,86</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,69; 15,97</t>
+          <t>5,78; 16,32</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,96; 23,11</t>
+          <t>11,03; 23,75</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14,14%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3,82%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4,18%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2,65%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 7,26</t>
+          <t>3,03; 10,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,87</t>
+          <t>2,29; 8,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,91</t>
+          <t>0,92; 5,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,31; 13,09</t>
+          <t>9,52; 20,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 10,2</t>
+          <t>1,64; 7,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 8,47</t>
+          <t>1,97; 7,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,24</t>
+          <t>1,02; 5,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,78; 21,37</t>
+          <t>4,7; 14,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,39</t>
+          <t>2,95; 7,72</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,86</t>
+          <t>2,77; 7,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,57</t>
+          <t>1,22; 4,67</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,93; 15,48</t>
+          <t>8,34; 15,92</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4,39%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4,35%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>5,85%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>2,85%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>4,3%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,39%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,44</t>
+          <t>4,29; 10,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,42</t>
+          <t>3,1; 9,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,13; 7,2</t>
+          <t>2,34; 7,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,3</t>
+          <t>1,95; 7,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,49; 11,06</t>
+          <t>3,37; 9,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,78</t>
+          <t>1,28; 5,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,37</t>
+          <t>2,09; 7,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,04; 8,41</t>
+          <t>0,37; 4,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,6; 8,79</t>
+          <t>4,51; 8,91</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,21</t>
+          <t>2,68; 6,18</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,84; 6,44</t>
+          <t>2,7; 6,52</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,15</t>
+          <t>1,76; 5,29</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8,36%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>5,97%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>4,7%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>4,56%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6,91%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,55</t>
+          <t>5,43; 8,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,28</t>
+          <t>4,81; 7,7</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,92</t>
+          <t>3,92; 6,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,13; 7,54</t>
+          <t>6,49; 10,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,41</t>
+          <t>4,59; 7,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,61</t>
+          <t>3,45; 6,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,98; 6,74</t>
+          <t>3,29; 6,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6,48; 10,51</t>
+          <t>4,66; 8,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,52; 7,67</t>
+          <t>5,46; 7,61</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,57</t>
+          <t>4,48; 6,52</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,97; 5,9</t>
+          <t>4,01; 5,92</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,56; 8,33</t>
+          <t>6,01; 8,58</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3753</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4694</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1263</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>3465</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4768</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4430</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3753</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4691</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4694</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8993</t>
+          <t>8454</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4357</t>
+          <t>1435; 7850</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1289; 7962</t>
+          <t>1646; 8860</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2030; 9428</t>
+          <t>1813; 9109</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1941; 9233</t>
+          <t>1784; 9200</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1504; 8554</t>
+          <t>0; 4224</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1741; 9928</t>
+          <t>1097; 7382</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1875; 10028</t>
+          <t>2043; 9192</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1960; 9775</t>
+          <t>1833; 8324</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2096; 10216</t>
+          <t>2202; 9430</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4210; 13846</t>
+          <t>4277; 13853</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5456; 16228</t>
+          <t>5069; 15657</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4861; 15101</t>
+          <t>4609; 13841</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5066</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6823</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5418</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6344</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3726</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>7306</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>5062</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7586</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5066</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6823</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5418</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>8032</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>14377</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1796; 7516</t>
+          <t>1997; 9445</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3993; 12660</t>
+          <t>3435; 11918</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2111; 10225</t>
+          <t>2363; 10167</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2576; 14067</t>
+          <t>2560; 12156</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2440; 9778</t>
+          <t>1248; 6915</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3358; 12103</t>
+          <t>3531; 12694</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2292; 11148</t>
+          <t>2213; 10507</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3237; 13866</t>
+          <t>4200; 14302</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5060; 14278</t>
+          <t>5014; 13904</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8577; 20719</t>
+          <t>8938; 21614</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5893; 17257</t>
+          <t>6304; 17161</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8254; 23401</t>
+          <t>8846; 21634</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,42 +2557,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3035</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3524</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3704</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>5075</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1419</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1458</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3035</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2279</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>3524</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>592</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4297</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2203; 9596</t>
+          <t>1162; 7136</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4834</t>
+          <t>643; 6184</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5155</t>
+          <t>1405; 7774</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2954</t>
+          <t>1764; 7930</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1156; 6769</t>
+          <t>2204; 10106</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>642; 6063</t>
+          <t>0; 4971</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1376; 7837</t>
+          <t>0; 4507</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1476; 7889</t>
+          <t>0; 2932</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4112; 13655</t>
+          <t>4719; 13470</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>990; 7980</t>
+          <t>1380; 9264</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2143; 9618</t>
+          <t>2113; 9762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1938; 9000</t>
+          <t>1849; 8717</t>
         </is>
       </c>
     </row>
@@ -2702,37 +2702,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9012</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5938</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6490</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4914</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>8405</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4081</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>5063</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3544</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9012</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5938</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6490</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>3786</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8700</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4743; 13443</t>
+          <t>5003; 14981</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1496; 9304</t>
+          <t>2827; 10526</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2323; 9255</t>
+          <t>3517; 11780</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>854; 8799</t>
+          <t>1287; 12886</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5414; 15040</t>
+          <t>4873; 13914</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3121; 10884</t>
+          <t>1471; 9417</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3443; 11443</t>
+          <t>2380; 9962</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1442; 13401</t>
+          <t>936; 9996</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12248; 24382</t>
+          <t>11691; 24538</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5723; 16598</t>
+          <t>5909; 16848</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6906; 18267</t>
+          <t>7095; 17630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3777; 16624</t>
+          <t>3876; 16990</t>
         </is>
       </c>
     </row>
@@ -2905,27 +2905,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2385</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2627</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3547</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>5278</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3227</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>662</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2627</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>5315</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2283; 10066</t>
+          <t>710; 6537</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>899; 7469</t>
+          <t>663; 6209</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4008</t>
+          <t>0; 3834</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>454; 4175</t>
+          <t>1156; 9098</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>709; 6332</t>
+          <t>2295; 9784</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>658; 6127</t>
+          <t>870; 7222</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3996</t>
+          <t>0; 2755</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1166; 10852</t>
+          <t>492; 4200</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4159; 13105</t>
+          <t>3914; 13042</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2834; 10798</t>
+          <t>2726; 10457</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 5128</t>
+          <t>0; 5104</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2594; 13145</t>
+          <t>2468; 11607</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>7510</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6892</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6650</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>8843</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2740</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>3191</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>4412</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6778</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>7510</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>6892</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6650</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>15758</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>700; 6232</t>
+          <t>4254; 12640</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1194; 7084</t>
+          <t>3556; 12350</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2019; 9765</t>
+          <t>3172; 12144</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3471; 11013</t>
+          <t>5223; 14652</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4408; 12817</t>
+          <t>700; 6484</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3648; 12156</t>
+          <t>1230; 6961</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3256; 12028</t>
+          <t>1736; 8732</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5571; 15903</t>
+          <t>3703; 11001</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6286; 15484</t>
+          <t>6002; 15632</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6000; 16199</t>
+          <t>5527; 16110</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6375; 17893</t>
+          <t>6475; 18280</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11214; 23650</t>
+          <t>10443; 22494</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>7609</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3524</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>19994</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>4909</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>5804</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>3645</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>9892</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>7609</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>7160</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>3524</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>10541</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>31109</t>
+          <t>30536</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2086; 9343</t>
+          <t>4105; 13679</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2722; 10920</t>
+          <t>3336; 12548</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1317; 8116</t>
+          <t>1320; 7679</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5360; 16298</t>
+          <t>13459; 29678</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4184; 13843</t>
+          <t>2111; 9912</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3874; 12349</t>
+          <t>2730; 10958</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1316; 7543</t>
+          <t>1398; 8159</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13703; 33343</t>
+          <t>5759; 17410</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7636; 19531</t>
+          <t>7797; 20407</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8052; 19500</t>
+          <t>7879; 20055</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3695; 12851</t>
+          <t>3435; 13152</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>22248; 43424</t>
+          <t>22015; 42008</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>11596</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>9257</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>7507</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>6931</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>9243</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>4695</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>7062</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>2084</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>11596</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>9257</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>7507</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9162</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5259; 14903</t>
+          <t>7032; 17640</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1962; 8929</t>
+          <t>5311; 16263</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3499; 11825</t>
+          <t>4004; 13209</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>601; 5656</t>
+          <t>3113; 12444</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7371; 18141</t>
+          <t>5321; 14980</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5349; 15035</t>
+          <t>2103; 9839</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4083; 12585</t>
+          <t>3432; 12219</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>3198; 13183</t>
+          <t>514; 6408</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>14826; 28285</t>
+          <t>14525; 28691</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>8860; 20858</t>
+          <t>9004; 20750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9519; 21580</t>
+          <t>9057; 21847</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>4606; 14856</t>
+          <t>5275; 15865</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>49967</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>45668</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>38600</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>58479</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>40639</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>33189</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>32132</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>36603</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>49967</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>45668</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>38600</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>62635</t>
+          <t>38120</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>99238</t>
+          <t>96599</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>30846; 51436</t>
+          <t>39235; 60973</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>24901; 44335</t>
+          <t>35965; 57637</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23611; 41695</t>
+          <t>29165; 49869</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27416; 50068</t>
+          <t>45376; 72397</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>39158; 60760</t>
+          <t>31291; 50830</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35045; 56959</t>
+          <t>24394; 43668</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29652; 50237</t>
+          <t>23158; 42850</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>49293; 79927</t>
+          <t>29234; 50580</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>77445; 107716</t>
+          <t>76611; 106770</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>65552; 95580</t>
+          <t>65194; 94771</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>57546; 85532</t>
+          <t>58078; 85840</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>79215; 118587</t>
+          <t>79789; 113760</t>
         </is>
       </c>
     </row>
